--- a/My_Professional_Reviews/UAS-5_Skor.xlsx
+++ b/My_Professional_Reviews/UAS-5_Skor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github3\2025_KIPP\asesmen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jonathankenanbudianto/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04162E76-CA32-4FBF-9F98-5B5AB9101282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1AF98F1-CDC6-3C41-927F-488F42632BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{8AFE3614-8754-EB4D-B44F-1C12FCF6F8C2}"/>
+    <workbookView xWindow="15800" yWindow="2360" windowWidth="13980" windowHeight="11460" firstSheet="1" activeTab="1" xr2:uid="{8AFE3614-8754-EB4D-B44F-1C12FCF6F8C2}"/>
   </bookViews>
   <sheets>
     <sheet name="UAS_1_My_Concepts" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="30">
   <si>
     <t>ID</t>
   </si>
@@ -118,6 +118,18 @@
   <si>
     <t>UAS-1_Usefulness</t>
   </si>
+  <si>
+    <t>Rachel Elnora Mannuelle S.</t>
+  </si>
+  <si>
+    <t>Ivant Samuel Silaban</t>
+  </si>
+  <si>
+    <t>Nashwa Kamila</t>
+  </si>
+  <si>
+    <t>Jonathan Kenan Budianto</t>
+  </si>
 </sst>
 </file>
 
@@ -182,12 +194,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -504,7 +517,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B73929F8-86DE-C24C-A270-AE251CD40D12}">
   <dimension ref="A1:AP82"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.6640625" style="2" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" style="2" customWidth="1"/>
@@ -512,7 +525,7 @@
     <col min="43" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -570,7 +583,7 @@
       <c r="AO1" s="1"/>
       <c r="AP1" s="1"/>
     </row>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -600,10 +613,28 @@
       <c r="AK2" s="3"/>
       <c r="AP2" s="3"/>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.75">
-      <c r="G3" s="4" t="str">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>13523139</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2">
+        <v>5</v>
+      </c>
+      <c r="F3" s="2">
+        <v>5</v>
+      </c>
+      <c r="G3" s="4">
         <f t="shared" ref="G3:G66" si="0">IF(COUNT(C3:F3)=0,"",AVERAGE(C3:F3))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="L3" s="4"/>
       <c r="Q3" s="4"/>
@@ -613,10 +644,28 @@
       <c r="AK3" s="4"/>
       <c r="AP3" s="4"/>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.75">
-      <c r="G4" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+    <row r="4" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A4" s="5">
+        <v>18224125</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="2">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2">
+        <v>5</v>
+      </c>
+      <c r="G4" s="4">
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="L4" s="4"/>
       <c r="Q4" s="4"/>
@@ -626,10 +675,28 @@
       <c r="AK4" s="4"/>
       <c r="AP4" s="4"/>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.75">
-      <c r="G5" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A5" s="5">
+        <v>13523129</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="2">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2">
+        <v>5</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2">
+        <v>5</v>
+      </c>
+      <c r="G5" s="4">
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="L5" s="4"/>
       <c r="Q5" s="4"/>
@@ -639,10 +706,28 @@
       <c r="AK5" s="4"/>
       <c r="AP5" s="4"/>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.75">
-      <c r="G6" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A6" s="5">
+        <v>14324017</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="2">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2">
+        <v>5</v>
+      </c>
+      <c r="G6" s="4">
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="L6" s="4"/>
       <c r="Q6" s="4"/>
@@ -652,7 +737,7 @@
       <c r="AK6" s="4"/>
       <c r="AP6" s="4"/>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G7" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -665,7 +750,7 @@
       <c r="AK7" s="4"/>
       <c r="AP7" s="4"/>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G8" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -678,7 +763,7 @@
       <c r="AK8" s="4"/>
       <c r="AP8" s="4"/>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G9" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -691,7 +776,7 @@
       <c r="AK9" s="4"/>
       <c r="AP9" s="4"/>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G10" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -704,7 +789,7 @@
       <c r="AK10" s="4"/>
       <c r="AP10" s="4"/>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G11" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -717,7 +802,7 @@
       <c r="AK11" s="4"/>
       <c r="AP11" s="4"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G12" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -730,7 +815,7 @@
       <c r="AK12" s="4"/>
       <c r="AP12" s="4"/>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G13" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -743,7 +828,7 @@
       <c r="AK13" s="4"/>
       <c r="AP13" s="4"/>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G14" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -756,7 +841,7 @@
       <c r="AK14" s="4"/>
       <c r="AP14" s="4"/>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G15" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -769,7 +854,7 @@
       <c r="AK15" s="4"/>
       <c r="AP15" s="4"/>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G16" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -782,7 +867,7 @@
       <c r="AK16" s="4"/>
       <c r="AP16" s="4"/>
     </row>
-    <row r="17" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="17" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G17" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -795,7 +880,7 @@
       <c r="AK17" s="4"/>
       <c r="AP17" s="4"/>
     </row>
-    <row r="18" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="18" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G18" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -808,7 +893,7 @@
       <c r="AK18" s="4"/>
       <c r="AP18" s="4"/>
     </row>
-    <row r="19" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="19" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G19" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -821,7 +906,7 @@
       <c r="AK19" s="4"/>
       <c r="AP19" s="4"/>
     </row>
-    <row r="20" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="20" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G20" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -834,7 +919,7 @@
       <c r="AK20" s="4"/>
       <c r="AP20" s="4"/>
     </row>
-    <row r="21" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="21" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G21" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -847,7 +932,7 @@
       <c r="AK21" s="4"/>
       <c r="AP21" s="4"/>
     </row>
-    <row r="22" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="22" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G22" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -860,7 +945,7 @@
       <c r="AK22" s="4"/>
       <c r="AP22" s="4"/>
     </row>
-    <row r="23" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="23" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G23" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -873,7 +958,7 @@
       <c r="AK23" s="4"/>
       <c r="AP23" s="4"/>
     </row>
-    <row r="24" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="24" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G24" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -886,7 +971,7 @@
       <c r="AK24" s="4"/>
       <c r="AP24" s="4"/>
     </row>
-    <row r="25" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="25" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G25" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -899,7 +984,7 @@
       <c r="AK25" s="4"/>
       <c r="AP25" s="4"/>
     </row>
-    <row r="26" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="26" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G26" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -912,7 +997,7 @@
       <c r="AK26" s="4"/>
       <c r="AP26" s="4"/>
     </row>
-    <row r="27" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="27" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G27" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -925,7 +1010,7 @@
       <c r="AK27" s="4"/>
       <c r="AP27" s="4"/>
     </row>
-    <row r="28" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="28" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G28" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -938,7 +1023,7 @@
       <c r="AK28" s="4"/>
       <c r="AP28" s="4"/>
     </row>
-    <row r="29" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="29" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G29" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -951,7 +1036,7 @@
       <c r="AK29" s="4"/>
       <c r="AP29" s="4"/>
     </row>
-    <row r="30" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="30" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G30" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -964,7 +1049,7 @@
       <c r="AK30" s="4"/>
       <c r="AP30" s="4"/>
     </row>
-    <row r="31" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="31" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G31" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -977,7 +1062,7 @@
       <c r="AK31" s="4"/>
       <c r="AP31" s="4"/>
     </row>
-    <row r="32" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="32" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G32" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -990,7 +1075,7 @@
       <c r="AK32" s="4"/>
       <c r="AP32" s="4"/>
     </row>
-    <row r="33" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="33" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G33" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1003,7 +1088,7 @@
       <c r="AK33" s="4"/>
       <c r="AP33" s="4"/>
     </row>
-    <row r="34" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="34" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G34" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1016,7 +1101,7 @@
       <c r="AK34" s="4"/>
       <c r="AP34" s="4"/>
     </row>
-    <row r="35" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="35" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G35" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1029,7 +1114,7 @@
       <c r="AK35" s="4"/>
       <c r="AP35" s="4"/>
     </row>
-    <row r="36" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="36" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G36" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1042,7 +1127,7 @@
       <c r="AK36" s="4"/>
       <c r="AP36" s="4"/>
     </row>
-    <row r="37" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="37" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G37" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1055,7 +1140,7 @@
       <c r="AK37" s="4"/>
       <c r="AP37" s="4"/>
     </row>
-    <row r="38" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="38" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G38" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1068,7 +1153,7 @@
       <c r="AK38" s="4"/>
       <c r="AP38" s="4"/>
     </row>
-    <row r="39" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="39" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G39" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1081,7 +1166,7 @@
       <c r="AK39" s="4"/>
       <c r="AP39" s="4"/>
     </row>
-    <row r="40" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="40" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G40" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1094,7 +1179,7 @@
       <c r="AK40" s="4"/>
       <c r="AP40" s="4"/>
     </row>
-    <row r="41" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="41" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G41" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1107,7 +1192,7 @@
       <c r="AK41" s="4"/>
       <c r="AP41" s="4"/>
     </row>
-    <row r="42" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="42" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G42" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1120,7 +1205,7 @@
       <c r="AK42" s="4"/>
       <c r="AP42" s="4"/>
     </row>
-    <row r="43" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="43" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G43" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1133,7 +1218,7 @@
       <c r="AK43" s="4"/>
       <c r="AP43" s="4"/>
     </row>
-    <row r="44" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="44" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G44" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1146,7 +1231,7 @@
       <c r="AK44" s="4"/>
       <c r="AP44" s="4"/>
     </row>
-    <row r="45" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="45" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G45" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1159,7 +1244,7 @@
       <c r="AK45" s="4"/>
       <c r="AP45" s="4"/>
     </row>
-    <row r="46" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="46" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G46" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1172,7 +1257,7 @@
       <c r="AK46" s="4"/>
       <c r="AP46" s="4"/>
     </row>
-    <row r="47" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="47" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G47" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1185,7 +1270,7 @@
       <c r="AK47" s="4"/>
       <c r="AP47" s="4"/>
     </row>
-    <row r="48" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="48" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G48" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1198,7 +1283,7 @@
       <c r="AK48" s="4"/>
       <c r="AP48" s="4"/>
     </row>
-    <row r="49" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="49" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G49" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1211,7 +1296,7 @@
       <c r="AK49" s="4"/>
       <c r="AP49" s="4"/>
     </row>
-    <row r="50" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="50" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G50" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1224,7 +1309,7 @@
       <c r="AK50" s="4"/>
       <c r="AP50" s="4"/>
     </row>
-    <row r="51" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="51" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G51" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1237,7 +1322,7 @@
       <c r="AK51" s="4"/>
       <c r="AP51" s="4"/>
     </row>
-    <row r="52" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="52" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G52" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1250,7 +1335,7 @@
       <c r="AK52" s="4"/>
       <c r="AP52" s="4"/>
     </row>
-    <row r="53" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="53" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G53" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1263,7 +1348,7 @@
       <c r="AK53" s="4"/>
       <c r="AP53" s="4"/>
     </row>
-    <row r="54" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="54" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G54" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1276,7 +1361,7 @@
       <c r="AK54" s="4"/>
       <c r="AP54" s="4"/>
     </row>
-    <row r="55" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="55" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G55" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1289,7 +1374,7 @@
       <c r="AK55" s="4"/>
       <c r="AP55" s="4"/>
     </row>
-    <row r="56" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="56" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G56" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1302,7 +1387,7 @@
       <c r="AK56" s="4"/>
       <c r="AP56" s="4"/>
     </row>
-    <row r="57" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="57" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G57" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1315,7 +1400,7 @@
       <c r="AK57" s="4"/>
       <c r="AP57" s="4"/>
     </row>
-    <row r="58" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="58" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G58" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1328,7 +1413,7 @@
       <c r="AK58" s="4"/>
       <c r="AP58" s="4"/>
     </row>
-    <row r="59" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="59" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G59" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1341,7 +1426,7 @@
       <c r="AK59" s="4"/>
       <c r="AP59" s="4"/>
     </row>
-    <row r="60" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="60" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G60" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1354,7 +1439,7 @@
       <c r="AK60" s="4"/>
       <c r="AP60" s="4"/>
     </row>
-    <row r="61" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="61" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G61" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1367,7 +1452,7 @@
       <c r="AK61" s="4"/>
       <c r="AP61" s="4"/>
     </row>
-    <row r="62" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="62" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G62" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1380,7 +1465,7 @@
       <c r="AK62" s="4"/>
       <c r="AP62" s="4"/>
     </row>
-    <row r="63" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="63" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G63" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1393,7 +1478,7 @@
       <c r="AK63" s="4"/>
       <c r="AP63" s="4"/>
     </row>
-    <row r="64" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="64" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G64" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1406,7 +1491,7 @@
       <c r="AK64" s="4"/>
       <c r="AP64" s="4"/>
     </row>
-    <row r="65" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="65" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G65" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1419,7 +1504,7 @@
       <c r="AK65" s="4"/>
       <c r="AP65" s="4"/>
     </row>
-    <row r="66" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="66" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G66" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1432,7 +1517,7 @@
       <c r="AK66" s="4"/>
       <c r="AP66" s="4"/>
     </row>
-    <row r="67" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="67" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G67" s="4" t="str">
         <f t="shared" ref="G67:G82" si="1">IF(COUNT(C67:F67)=0,"",AVERAGE(C67:F67))</f>
         <v/>
@@ -1445,7 +1530,7 @@
       <c r="AK67" s="4"/>
       <c r="AP67" s="4"/>
     </row>
-    <row r="68" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="68" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G68" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1458,7 +1543,7 @@
       <c r="AK68" s="4"/>
       <c r="AP68" s="4"/>
     </row>
-    <row r="69" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="69" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G69" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1471,7 +1556,7 @@
       <c r="AK69" s="4"/>
       <c r="AP69" s="4"/>
     </row>
-    <row r="70" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="70" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G70" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1484,7 +1569,7 @@
       <c r="AK70" s="4"/>
       <c r="AP70" s="4"/>
     </row>
-    <row r="71" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="71" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G71" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1497,7 +1582,7 @@
       <c r="AK71" s="4"/>
       <c r="AP71" s="4"/>
     </row>
-    <row r="72" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="72" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G72" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1510,7 +1595,7 @@
       <c r="AK72" s="4"/>
       <c r="AP72" s="4"/>
     </row>
-    <row r="73" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="73" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G73" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1523,7 +1608,7 @@
       <c r="AK73" s="4"/>
       <c r="AP73" s="4"/>
     </row>
-    <row r="74" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="74" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G74" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1536,7 +1621,7 @@
       <c r="AK74" s="4"/>
       <c r="AP74" s="4"/>
     </row>
-    <row r="75" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="75" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G75" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1549,7 +1634,7 @@
       <c r="AK75" s="4"/>
       <c r="AP75" s="4"/>
     </row>
-    <row r="76" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="76" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G76" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1562,7 +1647,7 @@
       <c r="AK76" s="4"/>
       <c r="AP76" s="4"/>
     </row>
-    <row r="77" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="77" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G77" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1575,7 +1660,7 @@
       <c r="AK77" s="4"/>
       <c r="AP77" s="4"/>
     </row>
-    <row r="78" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="78" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G78" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1588,7 +1673,7 @@
       <c r="AK78" s="4"/>
       <c r="AP78" s="4"/>
     </row>
-    <row r="79" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="79" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G79" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1601,7 +1686,7 @@
       <c r="AK79" s="4"/>
       <c r="AP79" s="4"/>
     </row>
-    <row r="80" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="80" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G80" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1614,7 +1699,7 @@
       <c r="AK80" s="4"/>
       <c r="AP80" s="4"/>
     </row>
-    <row r="81" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="81" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G81" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1627,7 +1712,7 @@
       <c r="AK81" s="4"/>
       <c r="AP81" s="4"/>
     </row>
-    <row r="82" spans="7:42" x14ac:dyDescent="0.75">
+    <row r="82" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G82" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -1654,7 +1739,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3204561E-E5BB-0640-805F-3DEAFF53B8FF}">
   <dimension ref="A1:AP82"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.6640625" style="2" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" style="2" customWidth="1"/>
@@ -1662,7 +1747,7 @@
     <col min="43" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1720,7 +1805,7 @@
       <c r="AO1" s="1"/>
       <c r="AP1" s="1"/>
     </row>
-    <row r="2" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -1750,10 +1835,28 @@
       <c r="AK2" s="3"/>
       <c r="AP2" s="3"/>
     </row>
-    <row r="3" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
-      <c r="G3" s="4" t="str">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>13523139</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2">
+        <v>5</v>
+      </c>
+      <c r="F3" s="2">
+        <v>5</v>
+      </c>
+      <c r="G3" s="4">
         <f t="shared" ref="G3:G66" si="0">IF(COUNT(C3:F3)=0,"",AVERAGE(C3:F3))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="L3" s="4"/>
       <c r="Q3" s="4"/>
@@ -1763,10 +1866,28 @@
       <c r="AK3" s="4"/>
       <c r="AP3" s="4"/>
     </row>
-    <row r="4" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
-      <c r="G4" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+    <row r="4" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A4" s="5">
+        <v>18224125</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="2">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2">
+        <v>5</v>
+      </c>
+      <c r="G4" s="4">
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="L4" s="4"/>
       <c r="Q4" s="4"/>
@@ -1776,10 +1897,28 @@
       <c r="AK4" s="4"/>
       <c r="AP4" s="4"/>
     </row>
-    <row r="5" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
-      <c r="G5" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A5" s="5">
+        <v>13523129</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="2">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2">
+        <v>5</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2">
+        <v>5</v>
+      </c>
+      <c r="G5" s="4">
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="L5" s="4"/>
       <c r="Q5" s="4"/>
@@ -1789,10 +1928,28 @@
       <c r="AK5" s="4"/>
       <c r="AP5" s="4"/>
     </row>
-    <row r="6" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
-      <c r="G6" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A6" s="5">
+        <v>14324017</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="2">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2">
+        <v>5</v>
+      </c>
+      <c r="G6" s="4">
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="L6" s="4"/>
       <c r="Q6" s="4"/>
@@ -1802,7 +1959,7 @@
       <c r="AK6" s="4"/>
       <c r="AP6" s="4"/>
     </row>
-    <row r="7" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G7" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1815,7 +1972,7 @@
       <c r="AK7" s="4"/>
       <c r="AP7" s="4"/>
     </row>
-    <row r="8" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G8" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1828,7 +1985,7 @@
       <c r="AK8" s="4"/>
       <c r="AP8" s="4"/>
     </row>
-    <row r="9" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G9" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1841,7 +1998,7 @@
       <c r="AK9" s="4"/>
       <c r="AP9" s="4"/>
     </row>
-    <row r="10" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G10" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1854,7 +2011,7 @@
       <c r="AK10" s="4"/>
       <c r="AP10" s="4"/>
     </row>
-    <row r="11" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G11" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1867,7 +2024,7 @@
       <c r="AK11" s="4"/>
       <c r="AP11" s="4"/>
     </row>
-    <row r="12" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G12" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1880,7 +2037,7 @@
       <c r="AK12" s="4"/>
       <c r="AP12" s="4"/>
     </row>
-    <row r="13" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G13" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1893,7 +2050,7 @@
       <c r="AK13" s="4"/>
       <c r="AP13" s="4"/>
     </row>
-    <row r="14" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G14" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1906,7 +2063,7 @@
       <c r="AK14" s="4"/>
       <c r="AP14" s="4"/>
     </row>
-    <row r="15" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G15" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1919,7 +2076,7 @@
       <c r="AK15" s="4"/>
       <c r="AP15" s="4"/>
     </row>
-    <row r="16" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G16" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1932,7 +2089,7 @@
       <c r="AK16" s="4"/>
       <c r="AP16" s="4"/>
     </row>
-    <row r="17" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="17" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G17" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1945,7 +2102,7 @@
       <c r="AK17" s="4"/>
       <c r="AP17" s="4"/>
     </row>
-    <row r="18" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="18" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G18" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1958,7 +2115,7 @@
       <c r="AK18" s="4"/>
       <c r="AP18" s="4"/>
     </row>
-    <row r="19" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="19" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G19" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1971,7 +2128,7 @@
       <c r="AK19" s="4"/>
       <c r="AP19" s="4"/>
     </row>
-    <row r="20" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="20" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G20" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1984,7 +2141,7 @@
       <c r="AK20" s="4"/>
       <c r="AP20" s="4"/>
     </row>
-    <row r="21" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="21" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G21" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -1997,7 +2154,7 @@
       <c r="AK21" s="4"/>
       <c r="AP21" s="4"/>
     </row>
-    <row r="22" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="22" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G22" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2010,7 +2167,7 @@
       <c r="AK22" s="4"/>
       <c r="AP22" s="4"/>
     </row>
-    <row r="23" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="23" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G23" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2023,7 +2180,7 @@
       <c r="AK23" s="4"/>
       <c r="AP23" s="4"/>
     </row>
-    <row r="24" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="24" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G24" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2036,7 +2193,7 @@
       <c r="AK24" s="4"/>
       <c r="AP24" s="4"/>
     </row>
-    <row r="25" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="25" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G25" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2049,7 +2206,7 @@
       <c r="AK25" s="4"/>
       <c r="AP25" s="4"/>
     </row>
-    <row r="26" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="26" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G26" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2062,7 +2219,7 @@
       <c r="AK26" s="4"/>
       <c r="AP26" s="4"/>
     </row>
-    <row r="27" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="27" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G27" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2075,7 +2232,7 @@
       <c r="AK27" s="4"/>
       <c r="AP27" s="4"/>
     </row>
-    <row r="28" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="28" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G28" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2088,7 +2245,7 @@
       <c r="AK28" s="4"/>
       <c r="AP28" s="4"/>
     </row>
-    <row r="29" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="29" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G29" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2101,7 +2258,7 @@
       <c r="AK29" s="4"/>
       <c r="AP29" s="4"/>
     </row>
-    <row r="30" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="30" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G30" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2114,7 +2271,7 @@
       <c r="AK30" s="4"/>
       <c r="AP30" s="4"/>
     </row>
-    <row r="31" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="31" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G31" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2127,7 +2284,7 @@
       <c r="AK31" s="4"/>
       <c r="AP31" s="4"/>
     </row>
-    <row r="32" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="32" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G32" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2140,7 +2297,7 @@
       <c r="AK32" s="4"/>
       <c r="AP32" s="4"/>
     </row>
-    <row r="33" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="33" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G33" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2153,7 +2310,7 @@
       <c r="AK33" s="4"/>
       <c r="AP33" s="4"/>
     </row>
-    <row r="34" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="34" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G34" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2166,7 +2323,7 @@
       <c r="AK34" s="4"/>
       <c r="AP34" s="4"/>
     </row>
-    <row r="35" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="35" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G35" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2179,7 +2336,7 @@
       <c r="AK35" s="4"/>
       <c r="AP35" s="4"/>
     </row>
-    <row r="36" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="36" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G36" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2192,7 +2349,7 @@
       <c r="AK36" s="4"/>
       <c r="AP36" s="4"/>
     </row>
-    <row r="37" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="37" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G37" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2205,7 +2362,7 @@
       <c r="AK37" s="4"/>
       <c r="AP37" s="4"/>
     </row>
-    <row r="38" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="38" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G38" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2218,7 +2375,7 @@
       <c r="AK38" s="4"/>
       <c r="AP38" s="4"/>
     </row>
-    <row r="39" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="39" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G39" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2231,7 +2388,7 @@
       <c r="AK39" s="4"/>
       <c r="AP39" s="4"/>
     </row>
-    <row r="40" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="40" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G40" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2244,7 +2401,7 @@
       <c r="AK40" s="4"/>
       <c r="AP40" s="4"/>
     </row>
-    <row r="41" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="41" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G41" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2257,7 +2414,7 @@
       <c r="AK41" s="4"/>
       <c r="AP41" s="4"/>
     </row>
-    <row r="42" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="42" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G42" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2270,7 +2427,7 @@
       <c r="AK42" s="4"/>
       <c r="AP42" s="4"/>
     </row>
-    <row r="43" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="43" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G43" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2283,7 +2440,7 @@
       <c r="AK43" s="4"/>
       <c r="AP43" s="4"/>
     </row>
-    <row r="44" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="44" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G44" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2296,7 +2453,7 @@
       <c r="AK44" s="4"/>
       <c r="AP44" s="4"/>
     </row>
-    <row r="45" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="45" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G45" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2309,7 +2466,7 @@
       <c r="AK45" s="4"/>
       <c r="AP45" s="4"/>
     </row>
-    <row r="46" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="46" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G46" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2322,7 +2479,7 @@
       <c r="AK46" s="4"/>
       <c r="AP46" s="4"/>
     </row>
-    <row r="47" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="47" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G47" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2335,7 +2492,7 @@
       <c r="AK47" s="4"/>
       <c r="AP47" s="4"/>
     </row>
-    <row r="48" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="48" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G48" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2348,7 +2505,7 @@
       <c r="AK48" s="4"/>
       <c r="AP48" s="4"/>
     </row>
-    <row r="49" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="49" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G49" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2361,7 +2518,7 @@
       <c r="AK49" s="4"/>
       <c r="AP49" s="4"/>
     </row>
-    <row r="50" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="50" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G50" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2374,7 +2531,7 @@
       <c r="AK50" s="4"/>
       <c r="AP50" s="4"/>
     </row>
-    <row r="51" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="51" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G51" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2387,7 +2544,7 @@
       <c r="AK51" s="4"/>
       <c r="AP51" s="4"/>
     </row>
-    <row r="52" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="52" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G52" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2400,7 +2557,7 @@
       <c r="AK52" s="4"/>
       <c r="AP52" s="4"/>
     </row>
-    <row r="53" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="53" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G53" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2413,7 +2570,7 @@
       <c r="AK53" s="4"/>
       <c r="AP53" s="4"/>
     </row>
-    <row r="54" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="54" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G54" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2426,7 +2583,7 @@
       <c r="AK54" s="4"/>
       <c r="AP54" s="4"/>
     </row>
-    <row r="55" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="55" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G55" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2439,7 +2596,7 @@
       <c r="AK55" s="4"/>
       <c r="AP55" s="4"/>
     </row>
-    <row r="56" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="56" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G56" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2452,7 +2609,7 @@
       <c r="AK56" s="4"/>
       <c r="AP56" s="4"/>
     </row>
-    <row r="57" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="57" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G57" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2465,7 +2622,7 @@
       <c r="AK57" s="4"/>
       <c r="AP57" s="4"/>
     </row>
-    <row r="58" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="58" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G58" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2478,7 +2635,7 @@
       <c r="AK58" s="4"/>
       <c r="AP58" s="4"/>
     </row>
-    <row r="59" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="59" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G59" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2491,7 +2648,7 @@
       <c r="AK59" s="4"/>
       <c r="AP59" s="4"/>
     </row>
-    <row r="60" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="60" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G60" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2504,7 +2661,7 @@
       <c r="AK60" s="4"/>
       <c r="AP60" s="4"/>
     </row>
-    <row r="61" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="61" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G61" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2517,7 +2674,7 @@
       <c r="AK61" s="4"/>
       <c r="AP61" s="4"/>
     </row>
-    <row r="62" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="62" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G62" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2530,7 +2687,7 @@
       <c r="AK62" s="4"/>
       <c r="AP62" s="4"/>
     </row>
-    <row r="63" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="63" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G63" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2543,7 +2700,7 @@
       <c r="AK63" s="4"/>
       <c r="AP63" s="4"/>
     </row>
-    <row r="64" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="64" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G64" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2556,7 +2713,7 @@
       <c r="AK64" s="4"/>
       <c r="AP64" s="4"/>
     </row>
-    <row r="65" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="65" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G65" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2569,7 +2726,7 @@
       <c r="AK65" s="4"/>
       <c r="AP65" s="4"/>
     </row>
-    <row r="66" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="66" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G66" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2582,7 +2739,7 @@
       <c r="AK66" s="4"/>
       <c r="AP66" s="4"/>
     </row>
-    <row r="67" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="67" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G67" s="4" t="str">
         <f t="shared" ref="G67:G82" si="1">IF(COUNT(C67:F67)=0,"",AVERAGE(C67:F67))</f>
         <v/>
@@ -2595,7 +2752,7 @@
       <c r="AK67" s="4"/>
       <c r="AP67" s="4"/>
     </row>
-    <row r="68" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="68" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G68" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2608,7 +2765,7 @@
       <c r="AK68" s="4"/>
       <c r="AP68" s="4"/>
     </row>
-    <row r="69" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="69" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G69" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2621,7 +2778,7 @@
       <c r="AK69" s="4"/>
       <c r="AP69" s="4"/>
     </row>
-    <row r="70" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="70" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G70" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2634,7 +2791,7 @@
       <c r="AK70" s="4"/>
       <c r="AP70" s="4"/>
     </row>
-    <row r="71" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="71" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G71" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2647,7 +2804,7 @@
       <c r="AK71" s="4"/>
       <c r="AP71" s="4"/>
     </row>
-    <row r="72" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="72" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G72" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2660,7 +2817,7 @@
       <c r="AK72" s="4"/>
       <c r="AP72" s="4"/>
     </row>
-    <row r="73" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="73" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G73" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2673,7 +2830,7 @@
       <c r="AK73" s="4"/>
       <c r="AP73" s="4"/>
     </row>
-    <row r="74" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="74" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G74" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2686,7 +2843,7 @@
       <c r="AK74" s="4"/>
       <c r="AP74" s="4"/>
     </row>
-    <row r="75" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="75" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G75" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2699,7 +2856,7 @@
       <c r="AK75" s="4"/>
       <c r="AP75" s="4"/>
     </row>
-    <row r="76" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="76" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G76" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2712,7 +2869,7 @@
       <c r="AK76" s="4"/>
       <c r="AP76" s="4"/>
     </row>
-    <row r="77" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="77" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G77" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2725,7 +2882,7 @@
       <c r="AK77" s="4"/>
       <c r="AP77" s="4"/>
     </row>
-    <row r="78" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="78" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G78" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2738,7 +2895,7 @@
       <c r="AK78" s="4"/>
       <c r="AP78" s="4"/>
     </row>
-    <row r="79" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="79" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G79" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2751,7 +2908,7 @@
       <c r="AK79" s="4"/>
       <c r="AP79" s="4"/>
     </row>
-    <row r="80" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="80" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G80" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2764,7 +2921,7 @@
       <c r="AK80" s="4"/>
       <c r="AP80" s="4"/>
     </row>
-    <row r="81" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="81" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G81" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2777,7 +2934,7 @@
       <c r="AK81" s="4"/>
       <c r="AP81" s="4"/>
     </row>
-    <row r="82" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="82" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G82" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -2804,7 +2961,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{118772BA-2C36-4B0B-9DD9-177CEE93B495}">
   <dimension ref="A1:AP82"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.6640625" style="2" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" style="2" customWidth="1"/>
@@ -2812,7 +2969,7 @@
     <col min="43" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2870,7 +3027,7 @@
       <c r="AO1" s="1"/>
       <c r="AP1" s="1"/>
     </row>
-    <row r="2" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -2900,10 +3057,28 @@
       <c r="AK2" s="3"/>
       <c r="AP2" s="3"/>
     </row>
-    <row r="3" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
-      <c r="G3" s="4" t="str">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>13523139</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2">
+        <v>5</v>
+      </c>
+      <c r="F3" s="2">
+        <v>5</v>
+      </c>
+      <c r="G3" s="4">
         <f t="shared" ref="G3:G66" si="0">IF(COUNT(C3:F3)=0,"",AVERAGE(C3:F3))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="L3" s="4"/>
       <c r="Q3" s="4"/>
@@ -2913,10 +3088,28 @@
       <c r="AK3" s="4"/>
       <c r="AP3" s="4"/>
     </row>
-    <row r="4" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
-      <c r="G4" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+    <row r="4" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A4" s="5">
+        <v>18224125</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="2">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2">
+        <v>5</v>
+      </c>
+      <c r="G4" s="4">
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="L4" s="4"/>
       <c r="Q4" s="4"/>
@@ -2926,10 +3119,28 @@
       <c r="AK4" s="4"/>
       <c r="AP4" s="4"/>
     </row>
-    <row r="5" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
-      <c r="G5" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A5" s="5">
+        <v>13523129</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="2">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2">
+        <v>5</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2">
+        <v>5</v>
+      </c>
+      <c r="G5" s="4">
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="L5" s="4"/>
       <c r="Q5" s="4"/>
@@ -2939,10 +3150,28 @@
       <c r="AK5" s="4"/>
       <c r="AP5" s="4"/>
     </row>
-    <row r="6" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
-      <c r="G6" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A6" s="5">
+        <v>14324017</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="2">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2">
+        <v>5</v>
+      </c>
+      <c r="G6" s="4">
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="L6" s="4"/>
       <c r="Q6" s="4"/>
@@ -2952,7 +3181,7 @@
       <c r="AK6" s="4"/>
       <c r="AP6" s="4"/>
     </row>
-    <row r="7" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G7" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2965,7 +3194,7 @@
       <c r="AK7" s="4"/>
       <c r="AP7" s="4"/>
     </row>
-    <row r="8" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G8" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2978,7 +3207,7 @@
       <c r="AK8" s="4"/>
       <c r="AP8" s="4"/>
     </row>
-    <row r="9" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G9" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2991,7 +3220,7 @@
       <c r="AK9" s="4"/>
       <c r="AP9" s="4"/>
     </row>
-    <row r="10" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G10" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3004,7 +3233,7 @@
       <c r="AK10" s="4"/>
       <c r="AP10" s="4"/>
     </row>
-    <row r="11" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G11" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3017,7 +3246,7 @@
       <c r="AK11" s="4"/>
       <c r="AP11" s="4"/>
     </row>
-    <row r="12" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G12" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3030,7 +3259,7 @@
       <c r="AK12" s="4"/>
       <c r="AP12" s="4"/>
     </row>
-    <row r="13" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G13" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3043,7 +3272,7 @@
       <c r="AK13" s="4"/>
       <c r="AP13" s="4"/>
     </row>
-    <row r="14" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G14" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3056,7 +3285,7 @@
       <c r="AK14" s="4"/>
       <c r="AP14" s="4"/>
     </row>
-    <row r="15" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G15" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3069,7 +3298,7 @@
       <c r="AK15" s="4"/>
       <c r="AP15" s="4"/>
     </row>
-    <row r="16" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G16" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3082,7 +3311,7 @@
       <c r="AK16" s="4"/>
       <c r="AP16" s="4"/>
     </row>
-    <row r="17" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="17" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G17" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3095,7 +3324,7 @@
       <c r="AK17" s="4"/>
       <c r="AP17" s="4"/>
     </row>
-    <row r="18" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="18" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G18" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3108,7 +3337,7 @@
       <c r="AK18" s="4"/>
       <c r="AP18" s="4"/>
     </row>
-    <row r="19" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="19" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G19" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3121,7 +3350,7 @@
       <c r="AK19" s="4"/>
       <c r="AP19" s="4"/>
     </row>
-    <row r="20" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="20" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G20" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3134,7 +3363,7 @@
       <c r="AK20" s="4"/>
       <c r="AP20" s="4"/>
     </row>
-    <row r="21" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="21" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G21" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3147,7 +3376,7 @@
       <c r="AK21" s="4"/>
       <c r="AP21" s="4"/>
     </row>
-    <row r="22" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="22" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G22" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3160,7 +3389,7 @@
       <c r="AK22" s="4"/>
       <c r="AP22" s="4"/>
     </row>
-    <row r="23" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="23" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G23" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3173,7 +3402,7 @@
       <c r="AK23" s="4"/>
       <c r="AP23" s="4"/>
     </row>
-    <row r="24" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="24" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G24" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3186,7 +3415,7 @@
       <c r="AK24" s="4"/>
       <c r="AP24" s="4"/>
     </row>
-    <row r="25" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="25" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G25" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3199,7 +3428,7 @@
       <c r="AK25" s="4"/>
       <c r="AP25" s="4"/>
     </row>
-    <row r="26" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="26" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G26" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3212,7 +3441,7 @@
       <c r="AK26" s="4"/>
       <c r="AP26" s="4"/>
     </row>
-    <row r="27" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="27" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G27" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3225,7 +3454,7 @@
       <c r="AK27" s="4"/>
       <c r="AP27" s="4"/>
     </row>
-    <row r="28" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="28" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G28" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3238,7 +3467,7 @@
       <c r="AK28" s="4"/>
       <c r="AP28" s="4"/>
     </row>
-    <row r="29" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="29" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G29" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3251,7 +3480,7 @@
       <c r="AK29" s="4"/>
       <c r="AP29" s="4"/>
     </row>
-    <row r="30" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="30" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G30" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3264,7 +3493,7 @@
       <c r="AK30" s="4"/>
       <c r="AP30" s="4"/>
     </row>
-    <row r="31" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="31" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G31" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3277,7 +3506,7 @@
       <c r="AK31" s="4"/>
       <c r="AP31" s="4"/>
     </row>
-    <row r="32" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="32" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G32" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3290,7 +3519,7 @@
       <c r="AK32" s="4"/>
       <c r="AP32" s="4"/>
     </row>
-    <row r="33" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="33" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G33" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3303,7 +3532,7 @@
       <c r="AK33" s="4"/>
       <c r="AP33" s="4"/>
     </row>
-    <row r="34" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="34" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G34" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3316,7 +3545,7 @@
       <c r="AK34" s="4"/>
       <c r="AP34" s="4"/>
     </row>
-    <row r="35" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="35" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G35" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3329,7 +3558,7 @@
       <c r="AK35" s="4"/>
       <c r="AP35" s="4"/>
     </row>
-    <row r="36" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="36" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G36" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3342,7 +3571,7 @@
       <c r="AK36" s="4"/>
       <c r="AP36" s="4"/>
     </row>
-    <row r="37" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="37" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G37" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3355,7 +3584,7 @@
       <c r="AK37" s="4"/>
       <c r="AP37" s="4"/>
     </row>
-    <row r="38" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="38" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G38" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3368,7 +3597,7 @@
       <c r="AK38" s="4"/>
       <c r="AP38" s="4"/>
     </row>
-    <row r="39" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="39" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G39" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3381,7 +3610,7 @@
       <c r="AK39" s="4"/>
       <c r="AP39" s="4"/>
     </row>
-    <row r="40" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="40" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G40" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3394,7 +3623,7 @@
       <c r="AK40" s="4"/>
       <c r="AP40" s="4"/>
     </row>
-    <row r="41" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="41" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G41" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3407,7 +3636,7 @@
       <c r="AK41" s="4"/>
       <c r="AP41" s="4"/>
     </row>
-    <row r="42" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="42" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G42" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3420,7 +3649,7 @@
       <c r="AK42" s="4"/>
       <c r="AP42" s="4"/>
     </row>
-    <row r="43" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="43" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G43" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3433,7 +3662,7 @@
       <c r="AK43" s="4"/>
       <c r="AP43" s="4"/>
     </row>
-    <row r="44" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="44" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G44" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3446,7 +3675,7 @@
       <c r="AK44" s="4"/>
       <c r="AP44" s="4"/>
     </row>
-    <row r="45" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="45" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G45" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3459,7 +3688,7 @@
       <c r="AK45" s="4"/>
       <c r="AP45" s="4"/>
     </row>
-    <row r="46" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="46" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G46" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3472,7 +3701,7 @@
       <c r="AK46" s="4"/>
       <c r="AP46" s="4"/>
     </row>
-    <row r="47" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="47" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G47" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3485,7 +3714,7 @@
       <c r="AK47" s="4"/>
       <c r="AP47" s="4"/>
     </row>
-    <row r="48" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="48" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G48" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3498,7 +3727,7 @@
       <c r="AK48" s="4"/>
       <c r="AP48" s="4"/>
     </row>
-    <row r="49" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="49" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G49" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3511,7 +3740,7 @@
       <c r="AK49" s="4"/>
       <c r="AP49" s="4"/>
     </row>
-    <row r="50" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="50" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G50" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3524,7 +3753,7 @@
       <c r="AK50" s="4"/>
       <c r="AP50" s="4"/>
     </row>
-    <row r="51" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="51" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G51" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3537,7 +3766,7 @@
       <c r="AK51" s="4"/>
       <c r="AP51" s="4"/>
     </row>
-    <row r="52" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="52" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G52" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3550,7 +3779,7 @@
       <c r="AK52" s="4"/>
       <c r="AP52" s="4"/>
     </row>
-    <row r="53" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="53" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G53" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3563,7 +3792,7 @@
       <c r="AK53" s="4"/>
       <c r="AP53" s="4"/>
     </row>
-    <row r="54" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="54" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G54" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3576,7 +3805,7 @@
       <c r="AK54" s="4"/>
       <c r="AP54" s="4"/>
     </row>
-    <row r="55" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="55" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G55" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3589,7 +3818,7 @@
       <c r="AK55" s="4"/>
       <c r="AP55" s="4"/>
     </row>
-    <row r="56" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="56" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G56" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3602,7 +3831,7 @@
       <c r="AK56" s="4"/>
       <c r="AP56" s="4"/>
     </row>
-    <row r="57" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="57" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G57" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3615,7 +3844,7 @@
       <c r="AK57" s="4"/>
       <c r="AP57" s="4"/>
     </row>
-    <row r="58" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="58" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G58" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3628,7 +3857,7 @@
       <c r="AK58" s="4"/>
       <c r="AP58" s="4"/>
     </row>
-    <row r="59" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="59" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G59" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3641,7 +3870,7 @@
       <c r="AK59" s="4"/>
       <c r="AP59" s="4"/>
     </row>
-    <row r="60" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="60" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G60" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3654,7 +3883,7 @@
       <c r="AK60" s="4"/>
       <c r="AP60" s="4"/>
     </row>
-    <row r="61" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="61" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G61" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3667,7 +3896,7 @@
       <c r="AK61" s="4"/>
       <c r="AP61" s="4"/>
     </row>
-    <row r="62" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="62" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G62" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3680,7 +3909,7 @@
       <c r="AK62" s="4"/>
       <c r="AP62" s="4"/>
     </row>
-    <row r="63" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="63" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G63" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3693,7 +3922,7 @@
       <c r="AK63" s="4"/>
       <c r="AP63" s="4"/>
     </row>
-    <row r="64" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="64" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G64" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3706,7 +3935,7 @@
       <c r="AK64" s="4"/>
       <c r="AP64" s="4"/>
     </row>
-    <row r="65" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="65" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G65" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3719,7 +3948,7 @@
       <c r="AK65" s="4"/>
       <c r="AP65" s="4"/>
     </row>
-    <row r="66" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="66" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G66" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3732,7 +3961,7 @@
       <c r="AK66" s="4"/>
       <c r="AP66" s="4"/>
     </row>
-    <row r="67" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="67" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G67" s="4" t="str">
         <f t="shared" ref="G67:G82" si="1">IF(COUNT(C67:F67)=0,"",AVERAGE(C67:F67))</f>
         <v/>
@@ -3745,7 +3974,7 @@
       <c r="AK67" s="4"/>
       <c r="AP67" s="4"/>
     </row>
-    <row r="68" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="68" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G68" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -3758,7 +3987,7 @@
       <c r="AK68" s="4"/>
       <c r="AP68" s="4"/>
     </row>
-    <row r="69" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="69" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G69" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -3771,7 +4000,7 @@
       <c r="AK69" s="4"/>
       <c r="AP69" s="4"/>
     </row>
-    <row r="70" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="70" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G70" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -3784,7 +4013,7 @@
       <c r="AK70" s="4"/>
       <c r="AP70" s="4"/>
     </row>
-    <row r="71" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="71" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G71" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -3797,7 +4026,7 @@
       <c r="AK71" s="4"/>
       <c r="AP71" s="4"/>
     </row>
-    <row r="72" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="72" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G72" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -3810,7 +4039,7 @@
       <c r="AK72" s="4"/>
       <c r="AP72" s="4"/>
     </row>
-    <row r="73" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="73" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G73" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -3823,7 +4052,7 @@
       <c r="AK73" s="4"/>
       <c r="AP73" s="4"/>
     </row>
-    <row r="74" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="74" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G74" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -3836,7 +4065,7 @@
       <c r="AK74" s="4"/>
       <c r="AP74" s="4"/>
     </row>
-    <row r="75" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="75" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G75" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -3849,7 +4078,7 @@
       <c r="AK75" s="4"/>
       <c r="AP75" s="4"/>
     </row>
-    <row r="76" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="76" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G76" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -3862,7 +4091,7 @@
       <c r="AK76" s="4"/>
       <c r="AP76" s="4"/>
     </row>
-    <row r="77" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="77" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G77" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -3875,7 +4104,7 @@
       <c r="AK77" s="4"/>
       <c r="AP77" s="4"/>
     </row>
-    <row r="78" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="78" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G78" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -3888,7 +4117,7 @@
       <c r="AK78" s="4"/>
       <c r="AP78" s="4"/>
     </row>
-    <row r="79" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="79" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G79" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -3901,7 +4130,7 @@
       <c r="AK79" s="4"/>
       <c r="AP79" s="4"/>
     </row>
-    <row r="80" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="80" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G80" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -3914,7 +4143,7 @@
       <c r="AK80" s="4"/>
       <c r="AP80" s="4"/>
     </row>
-    <row r="81" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="81" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G81" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -3927,7 +4156,7 @@
       <c r="AK81" s="4"/>
       <c r="AP81" s="4"/>
     </row>
-    <row r="82" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="82" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G82" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -3954,7 +4183,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50D1F948-1ADF-4B33-979B-06CD398BC5BF}">
   <dimension ref="A1:AP82"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.6640625" style="2" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" style="2" customWidth="1"/>
@@ -3962,7 +4191,7 @@
     <col min="43" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4020,7 +4249,7 @@
       <c r="AO1" s="1"/>
       <c r="AP1" s="1"/>
     </row>
-    <row r="2" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -4050,10 +4279,28 @@
       <c r="AK2" s="3"/>
       <c r="AP2" s="3"/>
     </row>
-    <row r="3" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
-      <c r="G3" s="4" t="str">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>13523139</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3" s="2">
+        <v>5</v>
+      </c>
+      <c r="E3" s="2">
+        <v>5</v>
+      </c>
+      <c r="F3" s="2">
+        <v>5</v>
+      </c>
+      <c r="G3" s="4">
         <f t="shared" ref="G3:G66" si="0">IF(COUNT(C3:F3)=0,"",AVERAGE(C3:F3))</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="L3" s="4"/>
       <c r="Q3" s="4"/>
@@ -4063,10 +4310,28 @@
       <c r="AK3" s="4"/>
       <c r="AP3" s="4"/>
     </row>
-    <row r="4" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
-      <c r="G4" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+    <row r="4" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A4" s="5">
+        <v>18224125</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="2">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2">
+        <v>5</v>
+      </c>
+      <c r="G4" s="4">
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="L4" s="4"/>
       <c r="Q4" s="4"/>
@@ -4076,10 +4341,28 @@
       <c r="AK4" s="4"/>
       <c r="AP4" s="4"/>
     </row>
-    <row r="5" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
-      <c r="G5" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A5" s="5">
+        <v>13523129</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="2">
+        <v>5</v>
+      </c>
+      <c r="D5" s="2">
+        <v>5</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2">
+        <v>5</v>
+      </c>
+      <c r="G5" s="4">
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="L5" s="4"/>
       <c r="Q5" s="4"/>
@@ -4089,10 +4372,28 @@
       <c r="AK5" s="4"/>
       <c r="AP5" s="4"/>
     </row>
-    <row r="6" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
-      <c r="G6" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A6" s="5">
+        <v>14324017</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="2">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2">
+        <v>5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2">
+        <v>5</v>
+      </c>
+      <c r="G6" s="4">
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
       <c r="L6" s="4"/>
       <c r="Q6" s="4"/>
@@ -4102,7 +4403,7 @@
       <c r="AK6" s="4"/>
       <c r="AP6" s="4"/>
     </row>
-    <row r="7" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G7" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4115,7 +4416,7 @@
       <c r="AK7" s="4"/>
       <c r="AP7" s="4"/>
     </row>
-    <row r="8" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G8" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4128,7 +4429,7 @@
       <c r="AK8" s="4"/>
       <c r="AP8" s="4"/>
     </row>
-    <row r="9" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G9" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4141,7 +4442,7 @@
       <c r="AK9" s="4"/>
       <c r="AP9" s="4"/>
     </row>
-    <row r="10" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G10" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4154,7 +4455,7 @@
       <c r="AK10" s="4"/>
       <c r="AP10" s="4"/>
     </row>
-    <row r="11" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G11" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4167,7 +4468,7 @@
       <c r="AK11" s="4"/>
       <c r="AP11" s="4"/>
     </row>
-    <row r="12" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G12" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4180,7 +4481,7 @@
       <c r="AK12" s="4"/>
       <c r="AP12" s="4"/>
     </row>
-    <row r="13" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G13" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4193,7 +4494,7 @@
       <c r="AK13" s="4"/>
       <c r="AP13" s="4"/>
     </row>
-    <row r="14" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G14" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4206,7 +4507,7 @@
       <c r="AK14" s="4"/>
       <c r="AP14" s="4"/>
     </row>
-    <row r="15" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G15" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4219,7 +4520,7 @@
       <c r="AK15" s="4"/>
       <c r="AP15" s="4"/>
     </row>
-    <row r="16" spans="1:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G16" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4232,7 +4533,7 @@
       <c r="AK16" s="4"/>
       <c r="AP16" s="4"/>
     </row>
-    <row r="17" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="17" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G17" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4245,7 +4546,7 @@
       <c r="AK17" s="4"/>
       <c r="AP17" s="4"/>
     </row>
-    <row r="18" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="18" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G18" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4258,7 +4559,7 @@
       <c r="AK18" s="4"/>
       <c r="AP18" s="4"/>
     </row>
-    <row r="19" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="19" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G19" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4271,7 +4572,7 @@
       <c r="AK19" s="4"/>
       <c r="AP19" s="4"/>
     </row>
-    <row r="20" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="20" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G20" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4284,7 +4585,7 @@
       <c r="AK20" s="4"/>
       <c r="AP20" s="4"/>
     </row>
-    <row r="21" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="21" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G21" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4297,7 +4598,7 @@
       <c r="AK21" s="4"/>
       <c r="AP21" s="4"/>
     </row>
-    <row r="22" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="22" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G22" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4310,7 +4611,7 @@
       <c r="AK22" s="4"/>
       <c r="AP22" s="4"/>
     </row>
-    <row r="23" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="23" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G23" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4323,7 +4624,7 @@
       <c r="AK23" s="4"/>
       <c r="AP23" s="4"/>
     </row>
-    <row r="24" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="24" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G24" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4336,7 +4637,7 @@
       <c r="AK24" s="4"/>
       <c r="AP24" s="4"/>
     </row>
-    <row r="25" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="25" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G25" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4349,7 +4650,7 @@
       <c r="AK25" s="4"/>
       <c r="AP25" s="4"/>
     </row>
-    <row r="26" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="26" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G26" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4362,7 +4663,7 @@
       <c r="AK26" s="4"/>
       <c r="AP26" s="4"/>
     </row>
-    <row r="27" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="27" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G27" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4375,7 +4676,7 @@
       <c r="AK27" s="4"/>
       <c r="AP27" s="4"/>
     </row>
-    <row r="28" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="28" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G28" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4388,7 +4689,7 @@
       <c r="AK28" s="4"/>
       <c r="AP28" s="4"/>
     </row>
-    <row r="29" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="29" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G29" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4401,7 +4702,7 @@
       <c r="AK29" s="4"/>
       <c r="AP29" s="4"/>
     </row>
-    <row r="30" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="30" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G30" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4414,7 +4715,7 @@
       <c r="AK30" s="4"/>
       <c r="AP30" s="4"/>
     </row>
-    <row r="31" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="31" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G31" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4427,7 +4728,7 @@
       <c r="AK31" s="4"/>
       <c r="AP31" s="4"/>
     </row>
-    <row r="32" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="32" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G32" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4440,7 +4741,7 @@
       <c r="AK32" s="4"/>
       <c r="AP32" s="4"/>
     </row>
-    <row r="33" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="33" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G33" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4453,7 +4754,7 @@
       <c r="AK33" s="4"/>
       <c r="AP33" s="4"/>
     </row>
-    <row r="34" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="34" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G34" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4466,7 +4767,7 @@
       <c r="AK34" s="4"/>
       <c r="AP34" s="4"/>
     </row>
-    <row r="35" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="35" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G35" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4479,7 +4780,7 @@
       <c r="AK35" s="4"/>
       <c r="AP35" s="4"/>
     </row>
-    <row r="36" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="36" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G36" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4492,7 +4793,7 @@
       <c r="AK36" s="4"/>
       <c r="AP36" s="4"/>
     </row>
-    <row r="37" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="37" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G37" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4505,7 +4806,7 @@
       <c r="AK37" s="4"/>
       <c r="AP37" s="4"/>
     </row>
-    <row r="38" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="38" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G38" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4518,7 +4819,7 @@
       <c r="AK38" s="4"/>
       <c r="AP38" s="4"/>
     </row>
-    <row r="39" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="39" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G39" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4531,7 +4832,7 @@
       <c r="AK39" s="4"/>
       <c r="AP39" s="4"/>
     </row>
-    <row r="40" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="40" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G40" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4544,7 +4845,7 @@
       <c r="AK40" s="4"/>
       <c r="AP40" s="4"/>
     </row>
-    <row r="41" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="41" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G41" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4557,7 +4858,7 @@
       <c r="AK41" s="4"/>
       <c r="AP41" s="4"/>
     </row>
-    <row r="42" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="42" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G42" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4570,7 +4871,7 @@
       <c r="AK42" s="4"/>
       <c r="AP42" s="4"/>
     </row>
-    <row r="43" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="43" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G43" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4583,7 +4884,7 @@
       <c r="AK43" s="4"/>
       <c r="AP43" s="4"/>
     </row>
-    <row r="44" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="44" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G44" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4596,7 +4897,7 @@
       <c r="AK44" s="4"/>
       <c r="AP44" s="4"/>
     </row>
-    <row r="45" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="45" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G45" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4609,7 +4910,7 @@
       <c r="AK45" s="4"/>
       <c r="AP45" s="4"/>
     </row>
-    <row r="46" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="46" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G46" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4622,7 +4923,7 @@
       <c r="AK46" s="4"/>
       <c r="AP46" s="4"/>
     </row>
-    <row r="47" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="47" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G47" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4635,7 +4936,7 @@
       <c r="AK47" s="4"/>
       <c r="AP47" s="4"/>
     </row>
-    <row r="48" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="48" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G48" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4648,7 +4949,7 @@
       <c r="AK48" s="4"/>
       <c r="AP48" s="4"/>
     </row>
-    <row r="49" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="49" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G49" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4661,7 +4962,7 @@
       <c r="AK49" s="4"/>
       <c r="AP49" s="4"/>
     </row>
-    <row r="50" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="50" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G50" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4674,7 +4975,7 @@
       <c r="AK50" s="4"/>
       <c r="AP50" s="4"/>
     </row>
-    <row r="51" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="51" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G51" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4687,7 +4988,7 @@
       <c r="AK51" s="4"/>
       <c r="AP51" s="4"/>
     </row>
-    <row r="52" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="52" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G52" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4700,7 +5001,7 @@
       <c r="AK52" s="4"/>
       <c r="AP52" s="4"/>
     </row>
-    <row r="53" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="53" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G53" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4713,7 +5014,7 @@
       <c r="AK53" s="4"/>
       <c r="AP53" s="4"/>
     </row>
-    <row r="54" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="54" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G54" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4726,7 +5027,7 @@
       <c r="AK54" s="4"/>
       <c r="AP54" s="4"/>
     </row>
-    <row r="55" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="55" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G55" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4739,7 +5040,7 @@
       <c r="AK55" s="4"/>
       <c r="AP55" s="4"/>
     </row>
-    <row r="56" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="56" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G56" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4752,7 +5053,7 @@
       <c r="AK56" s="4"/>
       <c r="AP56" s="4"/>
     </row>
-    <row r="57" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="57" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G57" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4765,7 +5066,7 @@
       <c r="AK57" s="4"/>
       <c r="AP57" s="4"/>
     </row>
-    <row r="58" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="58" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G58" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4778,7 +5079,7 @@
       <c r="AK58" s="4"/>
       <c r="AP58" s="4"/>
     </row>
-    <row r="59" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="59" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G59" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4791,7 +5092,7 @@
       <c r="AK59" s="4"/>
       <c r="AP59" s="4"/>
     </row>
-    <row r="60" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="60" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G60" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4804,7 +5105,7 @@
       <c r="AK60" s="4"/>
       <c r="AP60" s="4"/>
     </row>
-    <row r="61" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="61" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G61" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4817,7 +5118,7 @@
       <c r="AK61" s="4"/>
       <c r="AP61" s="4"/>
     </row>
-    <row r="62" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="62" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G62" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4830,7 +5131,7 @@
       <c r="AK62" s="4"/>
       <c r="AP62" s="4"/>
     </row>
-    <row r="63" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="63" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G63" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4843,7 +5144,7 @@
       <c r="AK63" s="4"/>
       <c r="AP63" s="4"/>
     </row>
-    <row r="64" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="64" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G64" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4856,7 +5157,7 @@
       <c r="AK64" s="4"/>
       <c r="AP64" s="4"/>
     </row>
-    <row r="65" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="65" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G65" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4869,7 +5170,7 @@
       <c r="AK65" s="4"/>
       <c r="AP65" s="4"/>
     </row>
-    <row r="66" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="66" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G66" s="4" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -4882,7 +5183,7 @@
       <c r="AK66" s="4"/>
       <c r="AP66" s="4"/>
     </row>
-    <row r="67" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="67" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G67" s="4" t="str">
         <f t="shared" ref="G67:G82" si="1">IF(COUNT(C67:F67)=0,"",AVERAGE(C67:F67))</f>
         <v/>
@@ -4895,7 +5196,7 @@
       <c r="AK67" s="4"/>
       <c r="AP67" s="4"/>
     </row>
-    <row r="68" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="68" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G68" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -4908,7 +5209,7 @@
       <c r="AK68" s="4"/>
       <c r="AP68" s="4"/>
     </row>
-    <row r="69" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="69" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G69" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -4921,7 +5222,7 @@
       <c r="AK69" s="4"/>
       <c r="AP69" s="4"/>
     </row>
-    <row r="70" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="70" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G70" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -4934,7 +5235,7 @@
       <c r="AK70" s="4"/>
       <c r="AP70" s="4"/>
     </row>
-    <row r="71" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="71" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G71" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -4947,7 +5248,7 @@
       <c r="AK71" s="4"/>
       <c r="AP71" s="4"/>
     </row>
-    <row r="72" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="72" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G72" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -4960,7 +5261,7 @@
       <c r="AK72" s="4"/>
       <c r="AP72" s="4"/>
     </row>
-    <row r="73" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="73" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G73" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -4973,7 +5274,7 @@
       <c r="AK73" s="4"/>
       <c r="AP73" s="4"/>
     </row>
-    <row r="74" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="74" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G74" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -4986,7 +5287,7 @@
       <c r="AK74" s="4"/>
       <c r="AP74" s="4"/>
     </row>
-    <row r="75" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="75" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G75" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -4999,7 +5300,7 @@
       <c r="AK75" s="4"/>
       <c r="AP75" s="4"/>
     </row>
-    <row r="76" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="76" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G76" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -5012,7 +5313,7 @@
       <c r="AK76" s="4"/>
       <c r="AP76" s="4"/>
     </row>
-    <row r="77" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="77" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G77" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -5025,7 +5326,7 @@
       <c r="AK77" s="4"/>
       <c r="AP77" s="4"/>
     </row>
-    <row r="78" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="78" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G78" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -5038,7 +5339,7 @@
       <c r="AK78" s="4"/>
       <c r="AP78" s="4"/>
     </row>
-    <row r="79" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="79" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G79" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -5051,7 +5352,7 @@
       <c r="AK79" s="4"/>
       <c r="AP79" s="4"/>
     </row>
-    <row r="80" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="80" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G80" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -5064,7 +5365,7 @@
       <c r="AK80" s="4"/>
       <c r="AP80" s="4"/>
     </row>
-    <row r="81" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="81" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G81" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
@@ -5077,7 +5378,7 @@
       <c r="AK81" s="4"/>
       <c r="AP81" s="4"/>
     </row>
-    <row r="82" spans="7:42" ht="14.75" x14ac:dyDescent="0.75">
+    <row r="82" spans="7:42" x14ac:dyDescent="0.2">
       <c r="G82" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
